--- a/data/tags/סינגלים חדשים/global/2026-01-week05/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-01-week05/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>מרסדס בנד – טינדר גירל</v>
+        <v>איתי בירמן – אין אהבה ללא כאב</v>
       </c>
       <c r="B2" t="str">
         <v>2026-01-29</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%9e%d7%a8%d7%a1%d7%93%d7%a1-%d7%91%d7%a0%d7%93-%d7%98%d7%99%d7%a0%d7%93%d7%a8-%d7%92%d7%99%d7%a8%d7%9c/</v>
+        <v>https://yosmusic.com/%d7%90%d7%99%d7%aa%d7%99-%d7%91%d7%99%d7%a8%d7%9e%d7%9f-%d7%90%d7%99%d7%9f-%d7%90%d7%94%d7%91%d7%94-%d7%9c%d7%9c%d7%90-%d7%9b%d7%90%d7%91/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-01-29</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>השיר "טינדר גירל" של מרסדס בנד מציג באופן אירוני, מלודי ולעיתים גם משעשע – אך בו־זמנית כואב – דיוקן של בדידות אנושית בעידן הדיגיטלי. מאחורי ההומור והקלילות המוזיקלית מסתתרת ביקורת חברתית עדינה על הדרך שבה טכנולוגיה, אפליקציות ואלגוריתמים מחליפים קשרים</v>
+        <v>השיר "אין אהבה ללא כאב" של איתי בקרמן הוא יצירה אישית, חשופה ובוגרת, שמצליחה להפוך סיפור משפחתי מורכב לבלדה רוקית מידטמפו בעלת עוצמה רגשית. זהו שיר שמתבונן באהבה לא כאגדה רומנטית, אלא כתהליך אנושי עמוק, רצוף סדקים, בחירות קשות ויכולת</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>מרסדס בנד – טינדר גירל</v>
+        <v>איתי בירמן – אין אהבה ללא כאב</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/global/2026-01-week05/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-01-week05/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L8"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>איתי בירמן – אין אהבה ללא כאב</v>
+        <v>יניב רם - כוחה של אמונה</v>
       </c>
       <c r="B2" t="str">
         <v>2026-01-29</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%99%d7%aa%d7%99-%d7%91%d7%99%d7%a8%d7%9e%d7%9f-%d7%90%d7%99%d7%9f-%d7%90%d7%94%d7%91%d7%94-%d7%9c%d7%9c%d7%90-%d7%9b%d7%90%d7%91/</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409407&amp;sid=5970a759bdaf153328e4dde9a385d228</v>
       </c>
       <c r="D2" t="str">
         <v>2026-01-29</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>השיר "אין אהבה ללא כאב" של איתי בקרמן הוא יצירה אישית, חשופה ובוגרת, שמצליחה להפוך סיפור משפחתי מורכב לבלדה רוקית מידטמפו בעלת עוצמה רגשית. זהו שיר שמתבונן באהבה לא כאגדה רומנטית, אלא כתהליך אנושי עמוק, רצוף סדקים, בחירות קשות ויכולת</v>
+        <v/>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,12 +469,240 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>איתי בירמן – אין אהבה ללא כאב</v>
+        <v>יניב רם - כוחה של אמונה</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>זואי קפלן - סיפור אחר</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-01-29</v>
+      </c>
+      <c r="C3" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409406&amp;sid=5970a759bdaf153328e4dde9a385d228</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-01-29</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>זואי קפלן - סיפור אחר</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>גיל קדלר - נשכבה</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-01-29</v>
+      </c>
+      <c r="C4" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409405&amp;sid=5970a759bdaf153328e4dde9a385d228</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-01-29</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>גיל קדלר - נשכבה</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>גבריאל דמרי - מחרוזת קצב של פעם 2026</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-01-29</v>
+      </c>
+      <c r="C5" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409404&amp;sid=5970a759bdaf153328e4dde9a385d228</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-01-29</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>גבריאל דמרי - מחרוזת קצב של פעם 2026</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>אליקם בוטה - תהיה מאושר</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-01-29</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409403&amp;sid=5970a759bdaf153328e4dde9a385d228</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-01-29</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>אליקם בוטה - תהיה מאושר</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>אליה רומנו - הילד הקטן שלך</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-01-29</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409402&amp;sid=5970a759bdaf153328e4dde9a385d228</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-01-29</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>אליה רומנו - הילד הקטן שלך</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>אלחנן אלחדד - תנגן את זה</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-01-29</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409401&amp;sid=5970a759bdaf153328e4dde9a385d228</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-01-29</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>אלחנן אלחדד - תנגן את זה</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L8"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-01-week05/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-01-week05/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:L5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>יניב רם - כוחה של אמונה</v>
+        <v>פרחי ירושלים - רני שב הביתה</v>
       </c>
       <c r="B2" t="str">
         <v>2026-01-29</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409407&amp;sid=5970a759bdaf153328e4dde9a385d228</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409411&amp;sid=c497b502b049ecd129e0847bcfcd5a46</v>
       </c>
       <c r="D2" t="str">
         <v>2026-01-29</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>יניב רם - כוחה של אמונה</v>
+        <v>פרחי ירושלים - רני שב הביתה</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>זואי קפלן - סיפור אחר</v>
+        <v>עופר לוי &amp; גילי זיגמן - מאוהב בגשם 2026</v>
       </c>
       <c r="B3" t="str">
         <v>2026-01-29</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409406&amp;sid=5970a759bdaf153328e4dde9a385d228</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409410&amp;sid=c497b502b049ecd129e0847bcfcd5a46</v>
       </c>
       <c r="D3" t="str">
         <v>2026-01-29</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>זואי קפלן - סיפור אחר</v>
+        <v>עופר לוי &amp; גילי זיגמן - מאוהב בגשם 2026</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>גיל קדלר - נשכבה</v>
+        <v>סיימון גרידיש - חמש לפנות בוקר</v>
       </c>
       <c r="B4" t="str">
         <v>2026-01-29</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409405&amp;sid=5970a759bdaf153328e4dde9a385d228</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409409&amp;sid=c497b502b049ecd129e0847bcfcd5a46</v>
       </c>
       <c r="D4" t="str">
         <v>2026-01-29</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>גיל קדלר - נשכבה</v>
+        <v>סיימון גרידיש - חמש לפנות בוקר</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>גבריאל דמרי - מחרוזת קצב של פעם 2026</v>
+        <v>יצחק גבריאל - מחרוזת שבת 2026</v>
       </c>
       <c r="B5" t="str">
         <v>2026-01-29</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409404&amp;sid=5970a759bdaf153328e4dde9a385d228</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409408&amp;sid=c497b502b049ecd129e0847bcfcd5a46</v>
       </c>
       <c r="D5" t="str">
         <v>2026-01-29</v>
@@ -583,126 +583,12 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>גבריאל דמרי - מחרוזת קצב של פעם 2026</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>אליקם בוטה - תהיה מאושר</v>
-      </c>
-      <c r="B6" t="str">
-        <v>2026-01-29</v>
-      </c>
-      <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409403&amp;sid=5970a759bdaf153328e4dde9a385d228</v>
-      </c>
-      <c r="D6" t="str">
-        <v>2026-01-29</v>
-      </c>
-      <c r="E6" t="str">
-        <v/>
-      </c>
-      <c r="F6" t="str">
-        <v/>
-      </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
-      <c r="H6" t="str">
-        <v/>
-      </c>
-      <c r="I6" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J6" t="str">
-        <v/>
-      </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
-      <c r="L6" t="str">
-        <v>אליקם בוטה - תהיה מאושר</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>אליה רומנו - הילד הקטן שלך</v>
-      </c>
-      <c r="B7" t="str">
-        <v>2026-01-29</v>
-      </c>
-      <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409402&amp;sid=5970a759bdaf153328e4dde9a385d228</v>
-      </c>
-      <c r="D7" t="str">
-        <v>2026-01-29</v>
-      </c>
-      <c r="E7" t="str">
-        <v/>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
-      <c r="I7" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J7" t="str">
-        <v/>
-      </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
-      <c r="L7" t="str">
-        <v>אליה רומנו - הילד הקטן שלך</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>אלחנן אלחדד - תנגן את זה</v>
-      </c>
-      <c r="B8" t="str">
-        <v>2026-01-29</v>
-      </c>
-      <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409401&amp;sid=5970a759bdaf153328e4dde9a385d228</v>
-      </c>
-      <c r="D8" t="str">
-        <v>2026-01-29</v>
-      </c>
-      <c r="E8" t="str">
-        <v/>
-      </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
-      <c r="H8" t="str">
-        <v/>
-      </c>
-      <c r="I8" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J8" t="str">
-        <v/>
-      </c>
-      <c r="K8" t="str">
-        <v/>
-      </c>
-      <c r="L8" t="str">
-        <v>אלחנן אלחדד - תנגן את זה</v>
+        <v>יצחק גבריאל - מחרוזת שבת 2026</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L8"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L5"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-01-week05/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-01-week05/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:L9"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>פרחי ירושלים - רני שב הביתה</v>
+        <v>מאור יפרח - ניסיתי מהלב 2</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-01-29</v>
+        <v>2026-01-30</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409411&amp;sid=c497b502b049ecd129e0847bcfcd5a46</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409420&amp;sid=c7d448190c80f69daa71470781758b56</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-01-29</v>
+        <v>2026-01-30</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>פרחי ירושלים - רני שב הביתה</v>
+        <v>מאור יפרח - ניסיתי מהלב 2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>עופר לוי &amp; גילי זיגמן - מאוהב בגשם 2026</v>
+        <v>מאור יפרח - את כאן לתמיד</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-01-29</v>
+        <v>2026-01-30</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409410&amp;sid=c497b502b049ecd129e0847bcfcd5a46</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409419&amp;sid=c7d448190c80f69daa71470781758b56</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-01-29</v>
+        <v>2026-01-30</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -507,21 +507,21 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>עופר לוי &amp; גילי זיגמן - מאוהב בגשם 2026</v>
+        <v>מאור יפרח - את כאן לתמיד</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>סיימון גרידיש - חמש לפנות בוקר</v>
+        <v>מאור יפרח - אבא בשמיים</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-01-29</v>
+        <v>2026-01-30</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409409&amp;sid=c497b502b049ecd129e0847bcfcd5a46</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409418&amp;sid=c7d448190c80f69daa71470781758b56</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-01-29</v>
+        <v>2026-01-30</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -545,21 +545,21 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>סיימון גרידיש - חמש לפנות בוקר</v>
+        <v>מאור יפרח - אבא בשמיים</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>יצחק גבריאל - מחרוזת שבת 2026</v>
+        <v>יגל יובל שרעבי - אביר על סוס לבן</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-01-29</v>
+        <v>2026-01-30</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409408&amp;sid=c497b502b049ecd129e0847bcfcd5a46</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409417&amp;sid=c7d448190c80f69daa71470781758b56</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-01-29</v>
+        <v>2026-01-30</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -583,12 +583,164 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>יצחק גבריאל - מחרוזת שבת 2026</v>
+        <v>יגל יובל שרעבי - אביר על סוס לבן</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>גאנגשמאנג מארחים את דוד אלדר - דוקטור</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-01-30</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409416&amp;sid=c7d448190c80f69daa71470781758b56</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-01-30</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>גאנגשמאנג מארחים את דוד אלדר - דוקטור</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>אורין כולב - הולכת לאיבוד</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-01-30</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409415&amp;sid=c7d448190c80f69daa71470781758b56</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-01-30</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>אורין כולב - הולכת לאיבוד</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>אוהד דוד לוי - ספטמבר</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-01-30</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409414&amp;sid=c7d448190c80f69daa71470781758b56</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-01-30</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>אוהד דוד לוי - ספטמבר</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>אבי ריימי &amp; יאיר בודנר מארחים את יהודה גלילי - לכו נרננה</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-01-30</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409413&amp;sid=c7d448190c80f69daa71470781758b56</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-01-30</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>אבי ריימי &amp; יאיר בודנר מארחים את יהודה גלילי - לכו נרננה</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L9"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-01-week05/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-01-week05/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>מאור יפרח - ניסיתי מהלב 2</v>
+        <v>קובי ממן - סיגריה אחרונה</v>
       </c>
       <c r="B2" t="str">
         <v>2026-01-30</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409420&amp;sid=c7d448190c80f69daa71470781758b56</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409423&amp;sid=66002cc5f41e639212beff12031784f0</v>
       </c>
       <c r="D2" t="str">
         <v>2026-01-30</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>מאור יפרח - ניסיתי מהלב 2</v>
+        <v>קובי ממן - סיגריה אחרונה</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>מאור יפרח - את כאן לתמיד</v>
+        <v>נחמן עמרמי - כמה טוב בלב</v>
       </c>
       <c r="B3" t="str">
         <v>2026-01-30</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409419&amp;sid=c7d448190c80f69daa71470781758b56</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409422&amp;sid=66002cc5f41e639212beff12031784f0</v>
       </c>
       <c r="D3" t="str">
         <v>2026-01-30</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>מאור יפרח - את כאן לתמיד</v>
+        <v>נחמן עמרמי - כמה טוב בלב</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>מאור יפרח - אבא בשמיים</v>
+        <v>מוטי שאלתיאל - ההילולה בתולאל</v>
       </c>
       <c r="B4" t="str">
         <v>2026-01-30</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409418&amp;sid=c7d448190c80f69daa71470781758b56</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409421&amp;sid=66002cc5f41e639212beff12031784f0</v>
       </c>
       <c r="D4" t="str">
         <v>2026-01-30</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>מאור יפרח - אבא בשמיים</v>
+        <v>מוטי שאלתיאל - ההילולה בתולאל</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>יגל יובל שרעבי - אביר על סוס לבן</v>
+        <v>פן חזות – בואי</v>
       </c>
       <c r="B5" t="str">
         <v>2026-01-30</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409417&amp;sid=c7d448190c80f69daa71470781758b56</v>
+        <v>https://yosmusic.com/%d7%a4%d7%9f-%d7%97%d7%96%d7%95%d7%aa-%d7%91%d7%95%d7%90%d7%99/</v>
       </c>
       <c r="D5" t="str">
         <v>2026-01-30</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v/>
+        <v>השיר "בואי" של פן חזות הוא דוגמה מובהקת לאיך פשטות יכולה להפוך לעוצמה. אין כאן יומרה פיוטית גבוהה או תחכום לשוני מורכב – ובדיוק בגלל זה השיר עובד. הוא נשמע כמו וידוי שקט, כמעט יומן אישי, שמוגש בלחישה רגשית יותר</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -583,164 +583,12 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>יגל יובל שרעבי - אביר על סוס לבן</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>גאנגשמאנג מארחים את דוד אלדר - דוקטור</v>
-      </c>
-      <c r="B6" t="str">
-        <v>2026-01-30</v>
-      </c>
-      <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409416&amp;sid=c7d448190c80f69daa71470781758b56</v>
-      </c>
-      <c r="D6" t="str">
-        <v>2026-01-30</v>
-      </c>
-      <c r="E6" t="str">
-        <v/>
-      </c>
-      <c r="F6" t="str">
-        <v/>
-      </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
-      <c r="H6" t="str">
-        <v/>
-      </c>
-      <c r="I6" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J6" t="str">
-        <v/>
-      </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
-      <c r="L6" t="str">
-        <v>גאנגשמאנג מארחים את דוד אלדר - דוקטור</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>אורין כולב - הולכת לאיבוד</v>
-      </c>
-      <c r="B7" t="str">
-        <v>2026-01-30</v>
-      </c>
-      <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409415&amp;sid=c7d448190c80f69daa71470781758b56</v>
-      </c>
-      <c r="D7" t="str">
-        <v>2026-01-30</v>
-      </c>
-      <c r="E7" t="str">
-        <v/>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
-      <c r="I7" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J7" t="str">
-        <v/>
-      </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
-      <c r="L7" t="str">
-        <v>אורין כולב - הולכת לאיבוד</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>אוהד דוד לוי - ספטמבר</v>
-      </c>
-      <c r="B8" t="str">
-        <v>2026-01-30</v>
-      </c>
-      <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409414&amp;sid=c7d448190c80f69daa71470781758b56</v>
-      </c>
-      <c r="D8" t="str">
-        <v>2026-01-30</v>
-      </c>
-      <c r="E8" t="str">
-        <v/>
-      </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
-      <c r="H8" t="str">
-        <v/>
-      </c>
-      <c r="I8" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J8" t="str">
-        <v/>
-      </c>
-      <c r="K8" t="str">
-        <v/>
-      </c>
-      <c r="L8" t="str">
-        <v>אוהד דוד לוי - ספטמבר</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>אבי ריימי &amp; יאיר בודנר מארחים את יהודה גלילי - לכו נרננה</v>
-      </c>
-      <c r="B9" t="str">
-        <v>2026-01-30</v>
-      </c>
-      <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409413&amp;sid=c7d448190c80f69daa71470781758b56</v>
-      </c>
-      <c r="D9" t="str">
-        <v>2026-01-30</v>
-      </c>
-      <c r="E9" t="str">
-        <v/>
-      </c>
-      <c r="F9" t="str">
-        <v/>
-      </c>
-      <c r="G9" t="str">
-        <v/>
-      </c>
-      <c r="H9" t="str">
-        <v/>
-      </c>
-      <c r="I9" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J9" t="str">
-        <v/>
-      </c>
-      <c r="K9" t="str">
-        <v/>
-      </c>
-      <c r="L9" t="str">
-        <v>אבי ריימי &amp; יאיר בודנר מארחים את יהודה גלילי - לכו נרננה</v>
+        <v>פן חזות – בואי</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L5"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-01-week05/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-01-week05/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:L2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>קובי ממן - סיגריה אחרונה</v>
+        <v>איילאו &amp; אופק אדנק – מעגל</v>
       </c>
       <c r="B2" t="str">
         <v>2026-01-30</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409423&amp;sid=66002cc5f41e639212beff12031784f0</v>
+        <v>https://yosmusic.com/%d7%90%d7%99%d7%99%d7%9c%d7%90%d7%95-%d7%90%d7%95%d7%a4%d7%a7-%d7%90%d7%93%d7%a0%d7%a7-%d7%9e%d7%a2%d7%92%d7%9c/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-01-30</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>השיר "מעגל" בביצוע אייאלו ואופק אדנק הוא הצהרת כוונות ברורה: שיר מסיבה דאנסהול־ראפ שנועד בראש ובראשונה להזיז גוף, לייצר אנרגיה קהילתית ולבנות רגע של חופש. הוא לא מתיימר להיות יצירה פיוטית עמוקה – והכנות הזו היא חלק מהחוזק שלו. המשפט</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,126 +469,12 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>קובי ממן - סיגריה אחרונה</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>נחמן עמרמי - כמה טוב בלב</v>
-      </c>
-      <c r="B3" t="str">
-        <v>2026-01-30</v>
-      </c>
-      <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409422&amp;sid=66002cc5f41e639212beff12031784f0</v>
-      </c>
-      <c r="D3" t="str">
-        <v>2026-01-30</v>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str">
-        <v>נחמן עמרמי - כמה טוב בלב</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>מוטי שאלתיאל - ההילולה בתולאל</v>
-      </c>
-      <c r="B4" t="str">
-        <v>2026-01-30</v>
-      </c>
-      <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409421&amp;sid=66002cc5f41e639212beff12031784f0</v>
-      </c>
-      <c r="D4" t="str">
-        <v>2026-01-30</v>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
-      <c r="L4" t="str">
-        <v>מוטי שאלתיאל - ההילולה בתולאל</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>פן חזות – בואי</v>
-      </c>
-      <c r="B5" t="str">
-        <v>2026-01-30</v>
-      </c>
-      <c r="C5" t="str">
-        <v>https://yosmusic.com/%d7%a4%d7%9f-%d7%97%d7%96%d7%95%d7%aa-%d7%91%d7%95%d7%90%d7%99/</v>
-      </c>
-      <c r="D5" t="str">
-        <v>2026-01-30</v>
-      </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
-      <c r="F5" t="str">
-        <v>השיר "בואי" של פן חזות הוא דוגמה מובהקת לאיך פשטות יכולה להפוך לעוצמה. אין כאן יומרה פיוטית גבוהה או תחכום לשוני מורכב – ובדיוק בגלל זה השיר עובד. הוא נשמע כמו וידוי שקט, כמעט יומן אישי, שמוגש בלחישה רגשית יותר</v>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J5" t="str">
-        <v/>
-      </c>
-      <c r="K5" t="str">
-        <v/>
-      </c>
-      <c r="L5" t="str">
-        <v>פן חזות – בואי</v>
+        <v>איילאו &amp; אופק אדנק – מעגל</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-01-week05/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-01-week05/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>איילאו &amp; אופק אדנק – מעגל</v>
+        <v>שי שלום - רק להיום</v>
       </c>
       <c r="B2" t="str">
         <v>2026-01-30</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%99%d7%99%d7%9c%d7%90%d7%95-%d7%90%d7%95%d7%a4%d7%a7-%d7%90%d7%93%d7%a0%d7%a7-%d7%9e%d7%a2%d7%92%d7%9c/</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409426&amp;sid=e152fc812c718c16af23893e38ed1407</v>
       </c>
       <c r="D2" t="str">
         <v>2026-01-30</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>השיר "מעגל" בביצוע אייאלו ואופק אדנק הוא הצהרת כוונות ברורה: שיר מסיבה דאנסהול־ראפ שנועד בראש ובראשונה להזיז גוף, לייצר אנרגיה קהילתית ולבנות רגע של חופש. הוא לא מתיימר להיות יצירה פיוטית עמוקה – והכנות הזו היא חלק מהחוזק שלו. המשפט</v>
+        <v/>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,12 +469,88 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>איילאו &amp; אופק אדנק – מעגל</v>
+        <v>שי שלום - רק להיום</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>שי שלום - מי ישיר לך</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-01-30</v>
+      </c>
+      <c r="C3" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409425&amp;sid=e152fc812c718c16af23893e38ed1407</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-01-30</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>שי שלום - מי ישיר לך</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>שי שלום - במיטה לבד</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-01-30</v>
+      </c>
+      <c r="C4" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409424&amp;sid=e152fc812c718c16af23893e38ed1407</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-01-30</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>שי שלום - במיטה לבד</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L4"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-01-week05/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-01-week05/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שי שלום - רק להיום</v>
+        <v>The Urban Tales Italian Diner ‏‫</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-01-30</v>
+        <v>2026-01-31</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409426&amp;sid=e152fc812c718c16af23893e38ed1407</v>
+        <v>https://yosmusic.com/the-urban-tales-italian-diner/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-01-30</v>
+        <v>2026-01-31</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>השיר Italian Diner של הלהקה הישראלית The Urban Tales הוא פצצת פאנק־רוק תעשייתי, שמערב אלימות מילולית, הומור שחור וגרוטסקה כדי לתאר חוויה יומיומית לכאורה – עבודת מלצרות – כסיוט קפקאי. מאחורי הזעם והכאוס מסתתרת אמירה ברורה על ניצול, הזנחה מערכתית,</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,88 +469,12 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שי שלום - רק להיום</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>שי שלום - מי ישיר לך</v>
-      </c>
-      <c r="B3" t="str">
-        <v>2026-01-30</v>
-      </c>
-      <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409425&amp;sid=e152fc812c718c16af23893e38ed1407</v>
-      </c>
-      <c r="D3" t="str">
-        <v>2026-01-30</v>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str">
-        <v>שי שלום - מי ישיר לך</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>שי שלום - במיטה לבד</v>
-      </c>
-      <c r="B4" t="str">
-        <v>2026-01-30</v>
-      </c>
-      <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409424&amp;sid=e152fc812c718c16af23893e38ed1407</v>
-      </c>
-      <c r="D4" t="str">
-        <v>2026-01-30</v>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
-      <c r="L4" t="str">
-        <v>שי שלום - במיטה לבד</v>
+        <v>The Urban Tales Italian Diner ‏‫</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
   </ignoredErrors>
 </worksheet>
 </file>